--- a/物联网/库存管理/呆滞库存/2025/8月物联卡呆滞物资-清理计划.xlsx
+++ b/物联网/库存管理/呆滞库存/2025/8月物联卡呆滞物资-清理计划.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\嘉兴移动\政企\物联网\库存管理\呆滞库存\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E1C5A9-F08D-44BA-9084-79AE5F712310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD06C80-CA4C-4AD2-8B1C-8B686B05613D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="945" yWindow="1140" windowWidth="27375" windowHeight="13950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4140" yWindow="870" windowWidth="21765" windowHeight="13950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -506,11 +506,11 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>朱昊翔</t>
+    <t>MP2工业级卡使用场景少，协调调货给需要使用的其他地市</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>MP2工业级卡使用场景少，协调调货给需要使用的其他地市</t>
+    <t>李增</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1110,7 +1110,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
@@ -1221,7 +1221,7 @@
       <c r="AN2" s="8"/>
       <c r="AO2" s="8"/>
     </row>
-    <row r="3" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
@@ -1330,7 +1330,7 @@
       <c r="AN3" s="8"/>
       <c r="AO3" s="8"/>
     </row>
-    <row r="4" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>75</v>
       </c>
@@ -1441,7 +1441,7 @@
       <c r="AN4" s="8"/>
       <c r="AO4" s="8"/>
     </row>
-    <row r="5" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>41</v>
       </c>
@@ -1550,7 +1550,7 @@
       <c r="AN5" s="8"/>
       <c r="AO5" s="8"/>
     </row>
-    <row r="6" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>41</v>
       </c>
@@ -1659,7 +1659,7 @@
       <c r="AN6" s="8"/>
       <c r="AO6" s="8"/>
     </row>
-    <row r="7" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
         <v>41</v>
       </c>
@@ -1876,16 +1876,16 @@
         <v>119</v>
       </c>
       <c r="AM8" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AN8" s="11">
         <v>46266</v>
       </c>
       <c r="AO8" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="9" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
         <v>41</v>
       </c>
@@ -1994,7 +1994,7 @@
       <c r="AN9" s="8"/>
       <c r="AO9" s="8"/>
     </row>
-    <row r="10" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
         <v>41</v>
       </c>
@@ -2105,7 +2105,7 @@
       <c r="AN10" s="8"/>
       <c r="AO10" s="8"/>
     </row>
-    <row r="11" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>41</v>
       </c>
@@ -2216,7 +2216,7 @@
       <c r="AN11" s="8"/>
       <c r="AO11" s="8"/>
     </row>
-    <row r="12" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
         <v>41</v>
       </c>
@@ -2327,7 +2327,7 @@
       <c r="AN12" s="8"/>
       <c r="AO12" s="8"/>
     </row>
-    <row r="13" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
         <v>41</v>
       </c>
@@ -2438,7 +2438,7 @@
       <c r="AN13" s="8"/>
       <c r="AO13" s="8"/>
     </row>
-    <row r="14" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
         <v>41</v>
       </c>
@@ -2549,7 +2549,7 @@
       <c r="AN14" s="8"/>
       <c r="AO14" s="8"/>
     </row>
-    <row r="15" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
         <v>75</v>
       </c>
@@ -2658,7 +2658,7 @@
       <c r="AN15" s="8"/>
       <c r="AO15" s="8"/>
     </row>
-    <row r="16" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
         <v>41</v>
       </c>
@@ -2767,7 +2767,7 @@
       <c r="AN16" s="8"/>
       <c r="AO16" s="8"/>
     </row>
-    <row r="17" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
         <v>41</v>
       </c>
@@ -2876,7 +2876,7 @@
       <c r="AN17" s="8"/>
       <c r="AO17" s="8"/>
     </row>
-    <row r="18" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
         <v>41</v>
       </c>
@@ -2985,7 +2985,7 @@
       <c r="AN18" s="8"/>
       <c r="AO18" s="8"/>
     </row>
-    <row r="19" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
         <v>75</v>
       </c>
@@ -3094,7 +3094,7 @@
       <c r="AN19" s="8"/>
       <c r="AO19" s="8"/>
     </row>
-    <row r="20" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
         <v>75</v>
       </c>
@@ -3203,7 +3203,7 @@
       <c r="AN20" s="8"/>
       <c r="AO20" s="8"/>
     </row>
-    <row r="21" spans="1:41" ht="85.5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:41" ht="71.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
         <v>75</v>
       </c>
